--- a/data/Lineups.xlsx
+++ b/data/Lineups.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Radical_stats\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Radical_stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93E3638-7FB0-4B32-8B57-086F6FFEE839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAD95F9-2B1E-4AE3-85A3-423639A9CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F8EDDAE-8367-4C64-A34D-358EA07D1A8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$S$124</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="32">
   <si>
     <t>Jam</t>
   </si>
@@ -44,22 +44,55 @@
     <t>Jammer</t>
   </si>
   <si>
+    <t>Jammer_Finish_jam_Box</t>
+  </si>
+  <si>
+    <t>Jammer_Start_jam_Box</t>
+  </si>
+  <si>
     <t>Pivot</t>
   </si>
   <si>
-    <t>Block_1</t>
+    <t>Pivot_Finish_jam_Box</t>
   </si>
   <si>
-    <t>Block_2</t>
+    <t>Pivot_Start_jam_Box</t>
   </si>
   <si>
-    <t>Block_3</t>
+    <t>Block_1</t>
   </si>
   <si>
     <t>Block_1_Finish_jam_Box</t>
   </si>
   <si>
     <t>Block_1_Start_jam_Box</t>
+  </si>
+  <si>
+    <t>Block_2</t>
+  </si>
+  <si>
+    <t>Block_2_Finish_jam_Box</t>
+  </si>
+  <si>
+    <t>Block_2_Start_jam_Box</t>
+  </si>
+  <si>
+    <t>Block_3</t>
+  </si>
+  <si>
+    <t>Block_3_Finish_jam_Box</t>
+  </si>
+  <si>
+    <t>Block_3_Start_jam_Box</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Rival</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
   <si>
     <t>16</t>
@@ -77,6 +110,9 @@
     <t>720</t>
   </si>
   <si>
+    <t>Pacha Mamis</t>
+  </si>
+  <si>
     <t>87</t>
   </si>
   <si>
@@ -92,40 +128,10 @@
     <t>1003</t>
   </si>
   <si>
-    <t>Jammer_Finish_jam_Box</t>
+    <t>Violet Attack</t>
   </si>
   <si>
-    <t>Jammer_Start_jam_Box</t>
-  </si>
-  <si>
-    <t>Pivot_Finish_jam_Box</t>
-  </si>
-  <si>
-    <t>Pivot_Start_jam_Box</t>
-  </si>
-  <si>
-    <t>Block_2_Finish_jam_Box</t>
-  </si>
-  <si>
-    <t>Block_2_Start_jam_Box</t>
-  </si>
-  <si>
-    <t>Block_3_Finish_jam_Box</t>
-  </si>
-  <si>
-    <t>Block_3_Start_jam_Box</t>
-  </si>
-  <si>
-    <t>Period</t>
-  </si>
-  <si>
-    <t>Rival</t>
-  </si>
-  <si>
-    <t>Pacha Mamis</t>
-  </si>
-  <si>
-    <t>Date</t>
+    <t>Fuego Latino</t>
   </si>
 </sst>
 </file>
@@ -497,8 +503,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF37986C-4D07-472A-A919-01F8D12E4AB0}">
-  <dimension ref="A1:S41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
@@ -521,55 +527,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -577,7 +583,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -586,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -595,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -604,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -613,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -625,7 +631,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S2" s="1">
         <v>45962</v>
@@ -636,7 +642,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -645,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -654,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -663,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -672,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -684,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S3" s="1">
         <v>45962</v>
@@ -695,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -704,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -713,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -722,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -731,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -743,7 +749,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S4" s="1">
         <v>45962</v>
@@ -754,7 +760,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -763,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -772,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -781,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -790,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -802,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S5" s="1">
         <v>45962</v>
@@ -813,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -822,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -831,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -840,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -849,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -861,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S6" s="1">
         <v>45962</v>
@@ -872,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -881,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -890,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -899,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -908,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -920,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S7" s="1">
         <v>45962</v>
@@ -931,7 +937,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -940,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -949,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -958,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -967,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -979,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S8" s="1">
         <v>45962</v>
@@ -990,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -999,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1008,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1017,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1026,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1038,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S9" s="1">
         <v>45962</v>
@@ -1049,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1058,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1067,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1076,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1085,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1097,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S10" s="1">
         <v>45962</v>
@@ -1108,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1117,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1126,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1135,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1144,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1156,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S11" s="1">
         <v>45962</v>
@@ -1167,7 +1173,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1176,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1185,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1194,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1203,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1215,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S12" s="1">
         <v>45962</v>
@@ -1226,7 +1232,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1235,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1244,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1253,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1262,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1274,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S13" s="1">
         <v>45962</v>
@@ -1285,7 +1291,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1294,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1303,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -1312,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1321,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1333,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S14" s="1">
         <v>45962</v>
@@ -1344,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1353,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1362,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1371,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1380,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1392,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S15" s="1">
         <v>45962</v>
@@ -1403,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1412,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1421,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1430,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1439,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1451,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S16" s="1">
         <v>45962</v>
@@ -1462,7 +1468,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1471,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1480,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1489,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1498,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1510,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S17" s="1">
         <v>45962</v>
@@ -1521,7 +1527,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1530,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1539,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1548,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1557,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1569,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S18" s="1">
         <v>45962</v>
@@ -1580,7 +1586,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1589,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1598,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1607,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1628,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S19" s="1">
         <v>45962</v>
@@ -1639,7 +1645,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1648,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1657,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1666,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1675,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1687,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S20" s="1">
         <v>45962</v>
@@ -1698,7 +1704,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1707,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1716,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1725,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -1734,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1746,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S21" s="1">
         <v>45962</v>
@@ -1757,7 +1763,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1766,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1775,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1784,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1793,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1805,7 +1811,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S22" s="1">
         <v>45962</v>
@@ -1816,7 +1822,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1825,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1834,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1843,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1852,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1864,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S23" s="1">
         <v>45962</v>
@@ -1875,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1884,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1893,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1902,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1911,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -1923,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S24" s="1">
         <v>45962</v>
@@ -1934,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1943,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1952,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1961,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1970,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1982,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S25" s="1">
         <v>45962</v>
@@ -1993,7 +1999,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2002,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2011,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2020,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2029,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -2041,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S26" s="1">
         <v>45962</v>
@@ -2052,7 +2058,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2061,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2070,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2079,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2088,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2100,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S27" s="1">
         <v>45962</v>
@@ -2111,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2120,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2129,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2138,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2147,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2159,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S28" s="1">
         <v>45962</v>
@@ -2170,7 +2176,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2179,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2188,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2197,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2206,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2218,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S29" s="1">
         <v>45962</v>
@@ -2229,7 +2235,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2238,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2247,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2256,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2265,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2277,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S30" s="1">
         <v>45962</v>
@@ -2288,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2297,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2306,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2315,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2324,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2336,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S31" s="1">
         <v>45962</v>
@@ -2347,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2356,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2365,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2374,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2383,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2395,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S32" s="1">
         <v>45962</v>
@@ -2406,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2415,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2424,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2433,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2442,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2454,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S33" s="1">
         <v>45962</v>
@@ -2465,7 +2471,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2474,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2483,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2492,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2501,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2513,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S34" s="1">
         <v>45962</v>
@@ -2524,7 +2530,7 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2533,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2542,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2551,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2560,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2572,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S35" s="1">
         <v>45962</v>
@@ -2583,7 +2589,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2592,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2601,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2610,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2619,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2631,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S36" s="1">
         <v>45962</v>
@@ -2642,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2651,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2660,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2669,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2678,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -2690,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S37" s="1">
         <v>45962</v>
@@ -2701,7 +2707,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2710,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2719,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2728,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2737,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2749,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S38" s="1">
         <v>45962</v>
@@ -2760,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2769,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2778,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2787,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2796,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2808,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S39" s="1">
         <v>45962</v>
@@ -2819,7 +2825,7 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2828,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2837,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2846,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2855,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2867,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S40" s="1">
         <v>45962</v>
@@ -2878,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2887,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2896,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2905,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2914,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2926,13 +2932,4911 @@
         <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S41" s="1">
         <v>45962</v>
       </c>
     </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42" t="s">
+        <v>30</v>
+      </c>
+      <c r="S42" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43" t="s">
+        <v>30</v>
+      </c>
+      <c r="S43" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>27</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44" t="s">
+        <v>30</v>
+      </c>
+      <c r="S44" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>30</v>
+      </c>
+      <c r="S45" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" t="s">
+        <v>30</v>
+      </c>
+      <c r="S46" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47" t="s">
+        <v>30</v>
+      </c>
+      <c r="S47" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48" t="s">
+        <v>30</v>
+      </c>
+      <c r="S48" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
+      <c r="R49" t="s">
+        <v>30</v>
+      </c>
+      <c r="S49" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>23</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50" t="s">
+        <v>30</v>
+      </c>
+      <c r="S50" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>20</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51" t="s">
+        <v>30</v>
+      </c>
+      <c r="S51" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>20</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+      <c r="R52" t="s">
+        <v>30</v>
+      </c>
+      <c r="S52" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>1</v>
+      </c>
+      <c r="R53" t="s">
+        <v>30</v>
+      </c>
+      <c r="S53" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>1</v>
+      </c>
+      <c r="R54" t="s">
+        <v>30</v>
+      </c>
+      <c r="S54" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55" t="s">
+        <v>30</v>
+      </c>
+      <c r="S55" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="R56" t="s">
+        <v>30</v>
+      </c>
+      <c r="S56" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>16</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="R57" t="s">
+        <v>30</v>
+      </c>
+      <c r="S57" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
+      </c>
+      <c r="N58" t="s">
+        <v>22</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="R58" t="s">
+        <v>30</v>
+      </c>
+      <c r="S58" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
+        <v>28</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="s">
+        <v>23</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>1</v>
+      </c>
+      <c r="R59" t="s">
+        <v>30</v>
+      </c>
+      <c r="S59" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>240</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>1</v>
+      </c>
+      <c r="R60" t="s">
+        <v>30</v>
+      </c>
+      <c r="S60" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>20</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>28</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>23</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>1</v>
+      </c>
+      <c r="R61" t="s">
+        <v>30</v>
+      </c>
+      <c r="S61" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>22</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>21</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62" t="s">
+        <v>30</v>
+      </c>
+      <c r="S62" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>28</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>22</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>1</v>
+      </c>
+      <c r="R63" t="s">
+        <v>30</v>
+      </c>
+      <c r="S63" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64" t="s">
+        <v>20</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64" t="s">
+        <v>30</v>
+      </c>
+      <c r="S64" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65" t="s">
+        <v>20</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65" t="s">
+        <v>30</v>
+      </c>
+      <c r="S65" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>27</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66" t="s">
+        <v>30</v>
+      </c>
+      <c r="S66" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>26</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67" t="s">
+        <v>28</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67" t="s">
+        <v>30</v>
+      </c>
+      <c r="S67" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68" t="s">
+        <v>28</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68" t="s">
+        <v>30</v>
+      </c>
+      <c r="S68" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69" t="s">
+        <v>30</v>
+      </c>
+      <c r="S69" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70" t="s">
+        <v>30</v>
+      </c>
+      <c r="S70" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>28</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71" t="s">
+        <v>30</v>
+      </c>
+      <c r="S71" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>26</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>28</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72" t="s">
+        <v>27</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72" t="s">
+        <v>30</v>
+      </c>
+      <c r="S72" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>28</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
+        <v>27</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73" t="s">
+        <v>30</v>
+      </c>
+      <c r="S73" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>26</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74" t="s">
+        <v>30</v>
+      </c>
+      <c r="S74" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>26</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>28</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75" t="s">
+        <v>27</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75" t="s">
+        <v>30</v>
+      </c>
+      <c r="S75" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
+        <v>26</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76" t="s">
+        <v>27</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76" t="s">
+        <v>30</v>
+      </c>
+      <c r="S76" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>13</v>
+      </c>
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
+        <v>26</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>28</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77" t="s">
+        <v>27</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77" t="s">
+        <v>30</v>
+      </c>
+      <c r="S77" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78" t="s">
+        <v>27</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78" t="s">
+        <v>30</v>
+      </c>
+      <c r="S78" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
+        <v>26</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
+        <v>22</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79" t="s">
+        <v>27</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79" t="s">
+        <v>30</v>
+      </c>
+      <c r="S79" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
+        <v>22</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>27</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80" t="s">
+        <v>30</v>
+      </c>
+      <c r="S80" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>17</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81" t="s">
+        <v>27</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81" t="s">
+        <v>30</v>
+      </c>
+      <c r="S81" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>18</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82" t="s">
+        <v>28</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82" t="s">
+        <v>30</v>
+      </c>
+      <c r="S82" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
+        <v>22</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83" t="s">
+        <v>27</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83" t="s">
+        <v>30</v>
+      </c>
+      <c r="S83" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>20</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84" t="s">
+        <v>30</v>
+      </c>
+      <c r="S84" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>21</v>
+      </c>
+      <c r="B85" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
+        <v>26</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>87</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>240</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85" t="s">
+        <v>30</v>
+      </c>
+      <c r="S85" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>22</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86" t="s">
+        <v>28</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86" t="s">
+        <v>27</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86" t="s">
+        <v>30</v>
+      </c>
+      <c r="S86" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>26</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87" t="s">
+        <v>22</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+      <c r="R87" t="s">
+        <v>31</v>
+      </c>
+      <c r="S87" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>2</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88" t="s">
+        <v>29</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88" t="s">
+        <v>21</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+      <c r="R88" t="s">
+        <v>31</v>
+      </c>
+      <c r="S88" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89" t="s">
+        <v>22</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89" t="s">
+        <v>29</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="R89" t="s">
+        <v>31</v>
+      </c>
+      <c r="S89" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90" t="s">
+        <v>22</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>1</v>
+      </c>
+      <c r="R90" t="s">
+        <v>31</v>
+      </c>
+      <c r="S90" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91" t="s">
+        <v>26</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>240</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91" t="s">
+        <v>22</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+      <c r="R91" t="s">
+        <v>31</v>
+      </c>
+      <c r="S91" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92" t="s">
+        <v>26</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" t="s">
+        <v>21</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92" t="s">
+        <v>22</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>1</v>
+      </c>
+      <c r="R92" t="s">
+        <v>31</v>
+      </c>
+      <c r="S92" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93" t="s">
+        <v>27</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93" t="s">
+        <v>29</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93" t="s">
+        <v>22</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>1</v>
+      </c>
+      <c r="R93" t="s">
+        <v>31</v>
+      </c>
+      <c r="S93" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94" t="s">
+        <v>26</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94" t="s">
+        <v>21</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>1</v>
+      </c>
+      <c r="R94" t="s">
+        <v>31</v>
+      </c>
+      <c r="S94" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>9</v>
+      </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95" t="s">
+        <v>21</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="R95" t="s">
+        <v>31</v>
+      </c>
+      <c r="S95" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="B96" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96" t="s">
+        <v>26</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96" t="s">
+        <v>22</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96" t="s">
+        <v>29</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="R96" t="s">
+        <v>31</v>
+      </c>
+      <c r="S96" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97" t="s">
+        <v>27</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+      <c r="R97" t="s">
+        <v>31</v>
+      </c>
+      <c r="S97" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98" t="s">
+        <v>28</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>1</v>
+      </c>
+      <c r="Q98">
+        <v>1</v>
+      </c>
+      <c r="R98" t="s">
+        <v>31</v>
+      </c>
+      <c r="S98" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>13</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99" t="s">
+        <v>27</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99" t="s">
+        <v>28</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>1</v>
+      </c>
+      <c r="R99" t="s">
+        <v>31</v>
+      </c>
+      <c r="S99" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>14</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100" t="s">
+        <v>28</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100" t="s">
+        <v>29</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100" t="s">
+        <v>22</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100" t="s">
+        <v>27</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>1</v>
+      </c>
+      <c r="R100" t="s">
+        <v>31</v>
+      </c>
+      <c r="S100" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>15</v>
+      </c>
+      <c r="B101">
+        <v>16</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>17</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>913</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>487</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>1003</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>1</v>
+      </c>
+      <c r="R101" t="s">
+        <v>31</v>
+      </c>
+      <c r="S101" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>16</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
+        <v>26</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>22</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102" t="s">
+        <v>29</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>1</v>
+      </c>
+      <c r="R102" t="s">
+        <v>31</v>
+      </c>
+      <c r="S102" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>17</v>
+      </c>
+      <c r="B103" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>26</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103" t="s">
+        <v>27</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103" t="s">
+        <v>21</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103" t="s">
+        <v>22</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>1</v>
+      </c>
+      <c r="R103" t="s">
+        <v>31</v>
+      </c>
+      <c r="S103" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
+        <v>22</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104" t="s">
+        <v>28</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="s">
+        <v>21</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>1</v>
+      </c>
+      <c r="R104" t="s">
+        <v>31</v>
+      </c>
+      <c r="S104" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
+        <v>26</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105" t="s">
+        <v>29</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" t="s">
+        <v>28</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105" t="s">
+        <v>21</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>1</v>
+      </c>
+      <c r="R105" t="s">
+        <v>31</v>
+      </c>
+      <c r="S105" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>20</v>
+      </c>
+      <c r="B106" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
+        <v>26</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106" t="s">
+        <v>28</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106" t="s">
+        <v>22</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>1</v>
+      </c>
+      <c r="R106" t="s">
+        <v>31</v>
+      </c>
+      <c r="S106" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>21</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107" t="s">
+        <v>28</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107" t="s">
+        <v>22</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>1</v>
+      </c>
+      <c r="R107" t="s">
+        <v>31</v>
+      </c>
+      <c r="S107" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108" t="s">
+        <v>26</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108" t="s">
+        <v>22</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>1</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108" t="s">
+        <v>31</v>
+      </c>
+      <c r="S108" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109" t="s">
+        <v>21</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109" t="s">
+        <v>31</v>
+      </c>
+      <c r="S109" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>3</v>
+      </c>
+      <c r="B110" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110" t="s">
+        <v>28</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110" t="s">
+        <v>27</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110" t="s">
+        <v>31</v>
+      </c>
+      <c r="S110" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>4</v>
+      </c>
+      <c r="B111" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" t="s">
+        <v>28</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111" t="s">
+        <v>27</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111" t="s">
+        <v>31</v>
+      </c>
+      <c r="S111" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112" t="s">
+        <v>28</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112" t="s">
+        <v>29</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112" t="s">
+        <v>22</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112" t="s">
+        <v>31</v>
+      </c>
+      <c r="S112" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113" t="s">
+        <v>28</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113" t="s">
+        <v>31</v>
+      </c>
+      <c r="S113" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>7</v>
+      </c>
+      <c r="B114" t="s">
+        <v>25</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114" t="s">
+        <v>29</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114" t="s">
+        <v>26</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114" t="s">
+        <v>31</v>
+      </c>
+      <c r="S114" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115" t="s">
+        <v>29</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115" t="s">
+        <v>27</v>
+      </c>
+      <c r="O115">
+        <v>1</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115" t="s">
+        <v>31</v>
+      </c>
+      <c r="S115" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116" t="s">
+        <v>29</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116" t="s">
+        <v>27</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116" t="s">
+        <v>26</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>0</v>
+      </c>
+      <c r="R116" t="s">
+        <v>31</v>
+      </c>
+      <c r="S116" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>10</v>
+      </c>
+      <c r="B117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117" t="s">
+        <v>21</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117" t="s">
+        <v>22</v>
+      </c>
+      <c r="O117">
+        <v>1</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>0</v>
+      </c>
+      <c r="R117" t="s">
+        <v>31</v>
+      </c>
+      <c r="S117" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
+        <v>28</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118" t="s">
+        <v>19</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118" t="s">
+        <v>22</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>1</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118" t="s">
+        <v>31</v>
+      </c>
+      <c r="S118" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" t="s">
+        <v>21</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119" t="s">
+        <v>22</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119" t="s">
+        <v>31</v>
+      </c>
+      <c r="S119" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>13</v>
+      </c>
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120" t="s">
+        <v>20</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120" t="s">
+        <v>29</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120" t="s">
+        <v>31</v>
+      </c>
+      <c r="S120" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>14</v>
+      </c>
+      <c r="B121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121" t="s">
+        <v>25</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121" t="s">
+        <v>29</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121" t="s">
+        <v>31</v>
+      </c>
+      <c r="S121" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>25</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
+        <v>28</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122" t="s">
+        <v>21</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122" t="s">
+        <v>29</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122" t="s">
+        <v>31</v>
+      </c>
+      <c r="S122" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>16</v>
+      </c>
+      <c r="B123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123" t="s">
+        <v>25</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123" t="s">
+        <v>22</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123" t="s">
+        <v>27</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123" t="s">
+        <v>31</v>
+      </c>
+      <c r="S123" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>17</v>
+      </c>
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124" t="s">
+        <v>28</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" t="s">
+        <v>22</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124" t="s">
+        <v>29</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124" t="s">
+        <v>31</v>
+      </c>
+      <c r="S124" s="1">
+        <v>45964</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:S124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>